--- a/output/pdf_financials_xlsx/ELEC.xlsx
+++ b/output/pdf_financials_xlsx/ELEC.xlsx
@@ -943,7 +943,7 @@
         <v>-0.031725</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.336419</v>
+        <v>-2.268419</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-1.903044</v>
@@ -1115,7 +1115,7 @@
         <v>-0.031725</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.302419</v>
+        <v>-2.302419</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-1.923044</v>
@@ -1217,7 +1217,7 @@
         <v>-0.031725</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.302419</v>
+        <v>-2.302419</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-1.923044</v>
@@ -1325,7 +1325,7 @@
         <v>1.58625</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>57.560475</v>
+        <v>-57.560475</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>96.15219999999999</v>
@@ -1359,7 +1359,7 @@
         <v>-0.031725</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.336419</v>
+        <v>-2.268419</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.903044</v>
@@ -1427,7 +1427,7 @@
         <v>-0.031725</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.336419</v>
+        <v>-2.268419</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.903044</v>
@@ -1507,7 +1507,7 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.455218434707131</v>
+        <v>-1.498841263452651</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-1.050947849865794</v>
@@ -3742,19 +3742,19 @@
         <v>0.025395</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.576621</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.605264</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.847251</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.145238</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.644152</v>
       </c>
     </row>
     <row r="93">
@@ -6521,7 +6521,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -7038,7 +7042,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7506,7 +7514,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -15307,7 +15319,7 @@
         </is>
       </c>
       <c r="I170" s="5" t="n">
-        <v>2.302419</v>
+        <v>-2.302419</v>
       </c>
       <c r="J170" s="5" t="n">
         <v>-1.923044</v>

--- a/output/pdf_financials_xlsx/ELEC.xlsx
+++ b/output/pdf_financials_xlsx/ELEC.xlsx
@@ -1581,19 +1581,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.00571</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.22599</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.194719</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.141559</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2.101875</v>
@@ -1608,7 +1606,7 @@
         <v>0.028082</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.839534</v>
       </c>
     </row>
     <row r="35">
@@ -1653,19 +1651,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.00571</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.22599</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.194719</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.141559</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2.101875</v>
@@ -1680,7 +1676,7 @@
         <v>0.028082</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.839534</v>
       </c>
     </row>
     <row r="37">
@@ -2094,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.194719</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.141559</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.06859999999999999</v>
@@ -2112,7 +2108,7 @@
         <v>0.175072</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.029602</v>
+        <v>0.190068</v>
       </c>
     </row>
     <row r="49">
@@ -4836,10 +4832,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009037999999999999</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004583</v>
       </c>
     </row>
     <row r="125">
@@ -4870,10 +4866,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009037999999999999</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004583</v>
       </c>
     </row>
     <row r="126">
@@ -5426,7 +5422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7821,7 +7817,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -8547,7 +8543,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -10797,7 +10793,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ELEC.xlsx
+++ b/output/pdf_financials_xlsx/ELEC.xlsx
@@ -1393,19 +1393,19 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.004542</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.006815</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.006815</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.006816</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.009075</v>
       </c>
     </row>
     <row r="29">
@@ -1427,19 +1427,19 @@
         <v>-0.031725</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.268419</v>
+        <v>-2.263877</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.903044</v>
+        <v>-1.896229</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.999277</v>
+        <v>-5.992462</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.550351</v>
+        <v>-6.543535</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-9.381487999999999</v>
+        <v>-9.372413</v>
       </c>
     </row>
     <row r="30">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-4798.999288062651</v>
+        <v>-4793.547767796434</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-59499.96366609137</v>
+        <v>-59438.05068580253</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-6414.824235710817</v>
+        <v>-6408.618980218398</v>
       </c>
     </row>
     <row r="31">
@@ -3999,19 +3999,19 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.004542</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.006815</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.006815</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.006816</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.009075</v>
       </c>
     </row>
     <row r="101">
@@ -9025,7 +9025,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ELEC.xlsx
+++ b/output/pdf_financials_xlsx/ELEC.xlsx
@@ -946,10 +946,10 @@
         <v>-2.268419</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.903044</v>
+        <v>-1.943044</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-5.999277</v>
+        <v>-5.979565</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-6.550351</v>
@@ -980,13 +980,13 @@
         <v>-0.034</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.019712</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.18873</v>
+        <v>-0.18873</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1362,10 +1362,10 @@
         <v>-2.268419</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.903044</v>
+        <v>-1.943044</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.999277</v>
+        <v>-5.979565</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-6.550351</v>
@@ -1430,10 +1430,10 @@
         <v>-2.263877</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.896229</v>
+        <v>-1.936229</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.992462</v>
+        <v>-5.97275</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-6.543535</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-4793.547767796434</v>
+        <v>-4777.779555399125</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-59438.05068580253</v>
@@ -1510,10 +1510,10 @@
         <v>-1.498841263452651</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-1.050947849865794</v>
+        <v>-1.029312769036625</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3296560870230527</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-2.881219647618883</v>
@@ -9784,7 +9784,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -13677,7 +13681,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
         <v>0.1</v>
       </c>
@@ -15236,7 +15244,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -15936,7 +15948,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -15997,7 +16013,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -16058,7 +16078,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -16721,7 +16745,11 @@
           <t>Current income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
